--- a/output/北塩原村_見込量の再算定_参考値.xlsx
+++ b/output/北塩原村_見込量の再算定_参考値.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -579,65 +579,77 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>村の給付の台帳の令和８年度の直近３か月の利用者数の平均（利用が数か月おきのサービスは月平均）。台帳の無いものは資料２－３の令和７年度</t>
+          <t>村の給付の台帳の令和８年度の直近３か月の利用者数の平均（利用が数か月おきのサービスは月平均）。台帳の無いものは資料２－３の令和７年度。サービスごとに台帳の最後の実績月が違うため、使った月を「起点の対象月」の列に示した</t>
         </is>
       </c>
     </row>
     <row r="8" ht="46" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>増減</t>
+          <t>１人当たりの利用量</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>卒業・年齢到達・地域移行・退院・退去は、村の回答が無く一人も確認できていないため０とした。参考値は「いまの利用が続いた場合」の値であり、令和９〜11年度は同じ値になる</t>
+          <t>台帳の利用日数÷利用者の延べ月数。起点と同じ月で出す（直近３か月）</t>
         </is>
       </c>
     </row>
     <row r="9" ht="46" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>計画相談支援</t>
+          <t>増減</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>国の基本指針の数え方（月間の利用者数）による。正本の表は年度の実人数で書いているため、参考に実人数も示す</t>
+          <t>卒業・年齢到達・地域移行・退院・退去は、村の回答が無く一人も確認できていないため０とした。参考値は「いまの利用が続いた場合」の値であり、令和９〜11年度は同じ値になる</t>
         </is>
       </c>
     </row>
     <row r="10" ht="46" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>計画の表に置く場合</t>
+          <t>計画相談支援</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>０を超え１に満たないものは１に切り上げ、それ以外は四捨五入</t>
+          <t>国の基本指針の数え方（月間の利用者数）による。正本の表は年度の実人数で書いているため、参考に実人数も示す</t>
         </is>
       </c>
     </row>
     <row r="11" ht="46" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>使い方</t>
+          <t>計画の表に置く場合</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>正本との差が大きいもの（色付き）は、正本が置いた増減の根拠を「02_確認できていない増減」の照会で確かめる。回答が出そろった段階で、一人ずつの積上げに置き換える</t>
+          <t>０を超え１に満たないものは１に切り上げ、それ以外は四捨五入</t>
         </is>
       </c>
     </row>
     <row r="12" ht="46" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t>使い方</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>正本との差が大きいもの（色付き）は、正本が置いた増減の根拠を「02_確認できていない増減」の照会で確かめる。回答が出そろった段階で、一人ずつの積上げに置き換える</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="46" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
           <t>含まないもの</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>供給できる量と未充足量（事業所の受入余力の照会Ｍ-24・Ｍ-25の回答が要る）、重度の方の内数（Ｍ-22・Ｍ-87）</t>
         </is>
@@ -658,7 +670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -671,7 +683,8 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="46" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -741,6 +754,11 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
+          <t>起点の対象月</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
           <t>確かめる照会</t>
         </is>
       </c>
@@ -784,7 +802,12 @@
           <t>台帳 令和８年度 直近３か月の平均</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>令和８年度 実施月6月〜8月（3か月）</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>Ｍ-89・Ｍ-15</t>
         </is>
@@ -829,7 +852,12 @@
           <t>１人当たり月11.6時間（資料２－３ 令和７年度 30.25時間÷2.6人）</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>令和８年度 実施月6月〜8月（3か月）</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>Ｍ-89</t>
         </is>
@@ -874,7 +902,12 @@
           <t>台帳 令和８年度 直近３か月の平均（うち４人は施設入所の方）</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>令和８年度 実施月7月〜9月（3か月）</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
         <is>
           <t>Ｍ-21・Ｍ-94</t>
         </is>
@@ -892,10 +925,10 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>108.6</v>
+        <v>100.7</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>118</v>
@@ -907,7 +940,7 @@
         <v>136</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>27.4</v>
+        <v>35.3</v>
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
@@ -916,10 +949,15 @@
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>１人当たり 台帳 令和８年度の利用日数÷延べ月数</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
+          <t>１人当たり 台帳 令和８年度 直近３か月の利用日数÷延べ月数</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>令和８年度 実施月7月〜9月（3か月）</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
         <is>
           <t>Ｍ-21</t>
         </is>
@@ -964,7 +1002,12 @@
           <t>台帳 令和８年度 直近３か月の平均</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>令和８年度 実施月6月〜8月（3か月）</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
         <is>
           <t>Ｍ-139</t>
         </is>
@@ -982,10 +1025,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>21.5</v>
+        <v>20.7</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>12</v>
@@ -997,7 +1040,7 @@
         <v>12</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-9.5</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="I11" s="10" t="inlineStr">
         <is>
@@ -1006,10 +1049,15 @@
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>１人当たり 台帳 令和８年度</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
+          <t>１人当たり 台帳 令和８年度 直近３か月</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>令和８年度 実施月6月〜8月（3か月）</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>Ｍ-139</t>
         </is>
@@ -1054,7 +1102,12 @@
           <t>資料２－３ 令和７年度（台帳なし）</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>―（資料２－３）</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
         <is>
           <t>Ｍ-137</t>
         </is>
@@ -1099,7 +1152,12 @@
           <t>台帳 令和８年度 直近３か月の平均</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>令和８年度 実施月4月〜6月（3か月）</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
         <is>
           <t>Ｍ-21</t>
         </is>
@@ -1117,10 +1175,10 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>209.8</v>
+        <v>211.7</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>200</v>
@@ -1132,7 +1190,7 @@
         <v>218</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-9.800000000000001</v>
+        <v>-11.7</v>
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
@@ -1141,10 +1199,15 @@
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>１人当たり 台帳 令和８年度</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
+          <t>１人当たり 台帳 令和８年度 直近３か月</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>令和８年度 実施月4月〜6月（3か月）</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
         <is>
           <t>Ｍ-21</t>
         </is>
@@ -1189,7 +1252,12 @@
           <t>台帳 令和８年度 利用を始めてからの２か月の平均</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>令和８年度 実施月7月〜8月（2か月）</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
         <is>
           <t>Ｍ-140</t>
         </is>
@@ -1234,7 +1302,12 @@
           <t>資料２－３ 令和６・７年度と台帳 令和８年度の月平均の３か年平均</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>令和８年度 実施月3月〜6月（4か月）</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
         <is>
           <t>Ｍ-139</t>
         </is>
@@ -1279,7 +1352,12 @@
           <t>同上（利用日数）</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>令和８年度 実施月3月〜6月（4か月）</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
         <is>
           <t>Ｍ-139</t>
         </is>
@@ -1324,7 +1402,12 @@
           <t>台帳 令和８年度 直近３か月の平均</t>
         </is>
       </c>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>令和８年度 実施月6月〜8月（3か月）</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
         <is>
           <t>Ｍ-139</t>
         </is>
@@ -1369,7 +1452,12 @@
           <t>台帳 令和８年度 直近３か月の平均</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>令和８年度 実施月7月〜9月（3か月）</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
         <is>
           <t>Ｍ-94</t>
         </is>
@@ -1414,7 +1502,12 @@
           <t>台帳 令和８年度 毎月の請求の人数の月平均（国の基本指針の数え方）</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>令和８年度 実施月3月〜7月（5か月）</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
         <is>
           <t>Ｍ-136</t>
         </is>
@@ -1459,7 +1552,12 @@
           <t>障がい児の台帳 令和８年度 直近３か月の平均</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>令和８年度 実施月6月〜8月（3か月）</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
         <is>
           <t>Ｍ-141</t>
         </is>
@@ -1477,10 +1575,10 @@
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>8</v>
@@ -1492,7 +1590,7 @@
         <v>8</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
@@ -1501,10 +1599,15 @@
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>１人当たり 障がい児の台帳 令和８年度</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="inlineStr">
+          <t>１人当たり 障がい児の台帳 令和８年度 直近３か月</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>令和８年度 実施月6月〜8月（3か月）</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
         <is>
           <t>Ｍ-139</t>
         </is>
@@ -1549,7 +1652,12 @@
           <t>障がい児の台帳 令和７年度 直近３か月の平均（令和８年度は見込みのみ）</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>令和７年度 実施月12月〜2月（3か月）</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
         <is>
           <t>Ｍ-137</t>
         </is>
@@ -1567,7 +1675,7 @@
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>9</v>
@@ -1582,7 +1690,7 @@
         <v>6</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-2.6</v>
+        <v>-3</v>
       </c>
       <c r="I24" s="10" t="inlineStr">
         <is>
@@ -1591,10 +1699,15 @@
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>１人当たり 障がい児の台帳 令和７年度</t>
-        </is>
-      </c>
-      <c r="K24" s="5" t="inlineStr">
+          <t>１人当たり 障がい児の台帳 令和７年度 直近３か月</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>令和７年度 実施月12月〜2月（3か月）</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
         <is>
           <t>Ｍ-137</t>
         </is>
@@ -1639,7 +1752,12 @@
           <t>障がい児の台帳 令和８年度の月平均</t>
         </is>
       </c>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>令和８年度 実施月3月〜7月（5か月）</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
         <is>
           <t>Ｍ-139</t>
         </is>
@@ -1684,7 +1802,12 @@
           <t>１人当たり 障がい児の台帳 令和８年度</t>
         </is>
       </c>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>令和８年度 実施月3月〜7月（5か月）</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
         <is>
           <t>Ｍ-139</t>
         </is>
@@ -1729,7 +1852,12 @@
           <t>障がい児の台帳 令和８年度 毎月の請求の人数の月平均</t>
         </is>
       </c>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>令和８年度 実施月3月〜7月（5か月）</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
         <is>
           <t>Ｍ-136・Ｍ-20</t>
         </is>
@@ -1766,6 +1894,11 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
+          <t>令和８年度 実施月3月〜7月（5か月）</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
           <t>Ｍ-136</t>
         </is>
       </c>
@@ -1801,14 +1934,19 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
+          <t>令和８年度 実施月3月〜7月（5か月）</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
           <t>Ｍ-136</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
